--- a/Incubations/PR vial count.xlsx
+++ b/Incubations/PR vial count.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\incubations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{344F725B-6953-46C4-80B0-3FF826EE68C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F434821D-2E0B-4BD1-9FA1-E4704966036E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{39C77E86-B1F0-4B34-AF37-F3D71B470EC0}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Synoptic" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Sites</t>
   </si>
@@ -73,10 +72,16 @@
     <t>Sampling times</t>
   </si>
   <si>
-    <t>Total GC/DOC</t>
-  </si>
-  <si>
     <t>Total HDPE</t>
+  </si>
+  <si>
+    <t>Total incubation</t>
+  </si>
+  <si>
+    <t>Total DOC</t>
+  </si>
+  <si>
+    <t>Total GC</t>
   </si>
 </sst>
 </file>
@@ -590,14 +595,14 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5">
         <f>A5*B5*C5*D5</f>
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="F5">
         <f>E5/C5</f>
@@ -626,11 +631,11 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <f>E5+Synoptic!D2</f>
-        <v>144</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -638,21 +643,35 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9">
         <f>Synoptic!D2+9*C5</f>
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <f>E5</f>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <f>(A5*B5*C5*2)+Synoptic!D2</f>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
